--- a/output/case_catalog.xlsx
+++ b/output/case_catalog.xlsx
@@ -21166,13 +21166,13 @@
         <v>2021</v>
       </c>
       <c r="G166">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H166">
         <v>117</v>
       </c>
       <c r="I166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J166" t="s">
         <v>1118</v>
@@ -21335,13 +21335,13 @@
         <v>2021</v>
       </c>
       <c r="G168">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H168">
         <v>127</v>
       </c>
       <c r="I168">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J168" t="s">
         <v>1107</v>
@@ -21433,13 +21433,13 @@
         <v>2021</v>
       </c>
       <c r="G169">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H169">
         <v>133</v>
       </c>
       <c r="I169">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J169" t="s">
         <v>1103</v>
@@ -21519,13 +21519,13 @@
         <v>2021</v>
       </c>
       <c r="G170">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H170">
         <v>138</v>
       </c>
       <c r="I170">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J170" t="s">
         <v>1114</v>
@@ -21617,13 +21617,13 @@
         <v>2021</v>
       </c>
       <c r="G171">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H171">
         <v>145</v>
       </c>
       <c r="I171">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J171" t="s">
         <v>1114</v>
@@ -21703,13 +21703,13 @@
         <v>2021</v>
       </c>
       <c r="G172">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H172">
         <v>150</v>
       </c>
       <c r="I172">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J172" t="s">
         <v>1093</v>
@@ -21789,13 +21789,13 @@
         <v>2021</v>
       </c>
       <c r="G173">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H173">
         <v>156</v>
       </c>
       <c r="I173">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J173" t="s">
         <v>1114</v>
@@ -21875,13 +21875,13 @@
         <v>2021</v>
       </c>
       <c r="G174">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H174">
         <v>165</v>
       </c>
       <c r="I174">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J174" t="s">
         <v>1103</v>
@@ -21973,13 +21973,13 @@
         <v>2021</v>
       </c>
       <c r="G175">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H175">
         <v>170</v>
       </c>
       <c r="I175">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J175" t="s">
         <v>1130</v>
@@ -22059,13 +22059,13 @@
         <v>2021</v>
       </c>
       <c r="G176">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H176">
         <v>175</v>
       </c>
       <c r="I176">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J176" t="s">
         <v>1130</v>
@@ -22228,13 +22228,13 @@
         <v>2021</v>
       </c>
       <c r="G178">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H178">
         <v>187</v>
       </c>
       <c r="I178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J178" t="s">
         <v>1118</v>
@@ -22326,13 +22326,13 @@
         <v>2021</v>
       </c>
       <c r="G179">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H179">
         <v>193</v>
       </c>
       <c r="I179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J179" t="s">
         <v>1114</v>
@@ -22412,13 +22412,13 @@
         <v>2021</v>
       </c>
       <c r="G180">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H180">
         <v>198</v>
       </c>
       <c r="I180">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J180" t="s">
         <v>1093</v>
@@ -22498,13 +22498,13 @@
         <v>2021</v>
       </c>
       <c r="G181">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H181">
         <v>204</v>
       </c>
       <c r="I181">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J181" t="s">
         <v>1093</v>
@@ -22584,13 +22584,13 @@
         <v>2021</v>
       </c>
       <c r="G182">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H182">
         <v>210</v>
       </c>
       <c r="I182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J182" t="s">
         <v>1103</v>
@@ -22670,13 +22670,13 @@
         <v>2021</v>
       </c>
       <c r="G183">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H183">
         <v>215</v>
       </c>
       <c r="I183">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J183" t="s">
         <v>1114</v>
@@ -22756,13 +22756,13 @@
         <v>2021</v>
       </c>
       <c r="G184">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H184">
         <v>219</v>
       </c>
       <c r="I184">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J184" t="s">
         <v>1118</v>
@@ -22842,13 +22842,13 @@
         <v>2021</v>
       </c>
       <c r="G185">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H185">
         <v>225</v>
       </c>
       <c r="I185">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J185" t="s">
         <v>1093</v>
@@ -22928,13 +22928,13 @@
         <v>2021</v>
       </c>
       <c r="G186">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H186">
         <v>229</v>
       </c>
       <c r="I186">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J186" t="s">
         <v>1112</v>
@@ -23112,13 +23112,13 @@
         <v>2021</v>
       </c>
       <c r="G188">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H188">
         <v>240</v>
       </c>
       <c r="I188">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J188" t="s">
         <v>1098</v>
@@ -23198,13 +23198,13 @@
         <v>2021</v>
       </c>
       <c r="G189">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H189">
         <v>244</v>
       </c>
       <c r="I189">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J189" t="s">
         <v>1103</v>
@@ -23284,13 +23284,13 @@
         <v>2021</v>
       </c>
       <c r="G190">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H190">
         <v>250</v>
       </c>
       <c r="I190">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J190" t="s">
         <v>1118</v>
@@ -23370,13 +23370,13 @@
         <v>2021</v>
       </c>
       <c r="G191">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H191">
         <v>256</v>
       </c>
       <c r="I191">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J191" t="s">
         <v>1103</v>
@@ -23456,13 +23456,13 @@
         <v>2021</v>
       </c>
       <c r="G192">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H192">
         <v>262</v>
       </c>
       <c r="I192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J192" t="s">
         <v>1093</v>
@@ -23542,13 +23542,13 @@
         <v>2021</v>
       </c>
       <c r="G193">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H193">
         <v>267</v>
       </c>
       <c r="I193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J193" t="s">
         <v>1103</v>
@@ -23628,13 +23628,13 @@
         <v>2021</v>
       </c>
       <c r="G194">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H194">
         <v>276</v>
       </c>
       <c r="I194">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J194" t="s">
         <v>1114</v>
@@ -23714,13 +23714,13 @@
         <v>2021</v>
       </c>
       <c r="G195">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H195">
         <v>280</v>
       </c>
       <c r="I195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J195" t="s">
         <v>1093</v>
@@ -23800,13 +23800,13 @@
         <v>2021</v>
       </c>
       <c r="G196">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H196">
         <v>285</v>
       </c>
       <c r="I196">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J196" t="s">
         <v>1093</v>
@@ -23886,13 +23886,13 @@
         <v>2021</v>
       </c>
       <c r="G197">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H197">
         <v>291</v>
       </c>
       <c r="I197">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J197" t="s">
         <v>1103</v>
@@ -23972,13 +23972,13 @@
         <v>2021</v>
       </c>
       <c r="G198">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H198">
         <v>301</v>
       </c>
       <c r="I198">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J198" t="s">
         <v>1111</v>
@@ -24070,13 +24070,13 @@
         <v>2021</v>
       </c>
       <c r="G199">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H199">
         <v>307</v>
       </c>
       <c r="I199">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J199" t="s">
         <v>1093</v>
@@ -24156,13 +24156,13 @@
         <v>2021</v>
       </c>
       <c r="G200">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H200">
         <v>318</v>
       </c>
       <c r="I200">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J200" t="s">
         <v>1103</v>
@@ -24242,13 +24242,13 @@
         <v>2021</v>
       </c>
       <c r="G201">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H201">
         <v>328</v>
       </c>
       <c r="I201">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J201" t="s">
         <v>1127</v>
@@ -24343,13 +24343,13 @@
         <v>2021</v>
       </c>
       <c r="G202">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H202">
         <v>335</v>
       </c>
       <c r="I202">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J202" t="s">
         <v>1093</v>
@@ -24429,13 +24429,13 @@
         <v>2021</v>
       </c>
       <c r="G203">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H203">
         <v>340</v>
       </c>
       <c r="I203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J203" t="s">
         <v>1114</v>
@@ -24515,13 +24515,13 @@
         <v>2021</v>
       </c>
       <c r="G204">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H204">
         <v>345</v>
       </c>
       <c r="I204">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J204" t="s">
         <v>1091</v>
@@ -24613,13 +24613,13 @@
         <v>2021</v>
       </c>
       <c r="G205">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H205">
         <v>352</v>
       </c>
       <c r="I205">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J205" t="s">
         <v>1093</v>
@@ -24699,13 +24699,13 @@
         <v>2021</v>
       </c>
       <c r="G206">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H206">
         <v>357</v>
       </c>
       <c r="I206">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J206" t="s">
         <v>1114</v>
@@ -24785,13 +24785,13 @@
         <v>2021</v>
       </c>
       <c r="G207">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H207">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="I207">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J207" t="s">
         <v>1116</v>

--- a/output/case_catalog.xlsx
+++ b/output/case_catalog.xlsx
@@ -3349,10 +3349,10 @@
     <t>Sports</t>
   </si>
   <si>
+    <t>Automotive</t>
+  </si>
+  <si>
     <t>Insurance</t>
-  </si>
-  <si>
-    <t>Automotive</t>
   </si>
   <si>
     <t>Profitability / Market Entry</t>
@@ -15252,7 +15252,7 @@
         <v>16</v>
       </c>
       <c r="J98" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K98" t="s">
         <v>1123</v>
@@ -15335,7 +15335,7 @@
         <v>18</v>
       </c>
       <c r="J99" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K99" t="s">
         <v>1136</v>
@@ -15418,7 +15418,7 @@
         <v>20</v>
       </c>
       <c r="J100" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K100" t="s">
         <v>1116</v>
@@ -15501,7 +15501,7 @@
         <v>18</v>
       </c>
       <c r="J101" t="s">
-        <v>1092</v>
+        <v>1106</v>
       </c>
       <c r="K101" t="s">
         <v>1137</v>
@@ -15584,7 +15584,7 @@
         <v>17</v>
       </c>
       <c r="J102" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="K102" t="s">
         <v>1125</v>
@@ -15667,7 +15667,7 @@
         <v>17</v>
       </c>
       <c r="J103" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K103" t="s">
         <v>1136</v>
@@ -15750,7 +15750,7 @@
         <v>19</v>
       </c>
       <c r="J104" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="K104" t="s">
         <v>1123</v>
@@ -15833,7 +15833,7 @@
         <v>16</v>
       </c>
       <c r="J105" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="K105" t="s">
         <v>1125</v>
@@ -15999,7 +15999,7 @@
         <v>16</v>
       </c>
       <c r="J107" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="K107" t="s">
         <v>1123</v>
@@ -16082,7 +16082,7 @@
         <v>18</v>
       </c>
       <c r="J108" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K108" t="s">
         <v>1119</v>
@@ -16165,7 +16165,7 @@
         <v>18</v>
       </c>
       <c r="J109" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="K109" t="s">
         <v>1119</v>
@@ -16248,7 +16248,7 @@
         <v>20</v>
       </c>
       <c r="J110" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K110" t="s">
         <v>1116</v>
@@ -16414,7 +16414,7 @@
         <v>16</v>
       </c>
       <c r="J112" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K112" t="s">
         <v>1136</v>
@@ -16497,7 +16497,7 @@
         <v>18</v>
       </c>
       <c r="J113" t="s">
-        <v>1092</v>
+        <v>1109</v>
       </c>
       <c r="K113" t="s">
         <v>1115</v>
@@ -16663,7 +16663,7 @@
         <v>18</v>
       </c>
       <c r="J115" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="K115" t="s">
         <v>1115</v>
@@ -16746,7 +16746,7 @@
         <v>16</v>
       </c>
       <c r="J116" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K116" t="s">
         <v>1123</v>
@@ -16829,7 +16829,7 @@
         <v>16</v>
       </c>
       <c r="J117" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K117" t="s">
         <v>1136</v>
@@ -16995,7 +16995,7 @@
         <v>16</v>
       </c>
       <c r="J119" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K119" t="s">
         <v>1123</v>
@@ -17078,7 +17078,7 @@
         <v>16</v>
       </c>
       <c r="J120" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K120" t="s">
         <v>1115</v>
@@ -17161,7 +17161,7 @@
         <v>16</v>
       </c>
       <c r="J121" t="s">
-        <v>1092</v>
+        <v>1111</v>
       </c>
       <c r="K121" t="s">
         <v>1115</v>
@@ -17244,7 +17244,7 @@
         <v>18</v>
       </c>
       <c r="J122" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K122" t="s">
         <v>1119</v>
@@ -17327,7 +17327,7 @@
         <v>17</v>
       </c>
       <c r="J123" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="K123" t="s">
         <v>1119</v>
@@ -17410,7 +17410,7 @@
         <v>18</v>
       </c>
       <c r="J124" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K124" t="s">
         <v>1136</v>
@@ -17493,7 +17493,7 @@
         <v>19</v>
       </c>
       <c r="J125" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="K125" t="s">
         <v>1115</v>
@@ -17576,7 +17576,7 @@
         <v>17</v>
       </c>
       <c r="J126" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K126" t="s">
         <v>1116</v>
@@ -17659,7 +17659,7 @@
         <v>18</v>
       </c>
       <c r="J127" t="s">
-        <v>1092</v>
+        <v>1111</v>
       </c>
       <c r="K127" t="s">
         <v>1116</v>
@@ -17825,7 +17825,7 @@
         <v>19</v>
       </c>
       <c r="J129" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="K129" t="s">
         <v>1136</v>
@@ -17908,7 +17908,7 @@
         <v>18</v>
       </c>
       <c r="J130" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="K130" t="s">
         <v>1139</v>
@@ -17991,7 +17991,7 @@
         <v>18</v>
       </c>
       <c r="J131" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K131" t="s">
         <v>1136</v>
@@ -18074,7 +18074,7 @@
         <v>21</v>
       </c>
       <c r="J132" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K132" t="s">
         <v>1115</v>
@@ -18157,7 +18157,7 @@
         <v>22</v>
       </c>
       <c r="J133" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="K133" t="s">
         <v>1123</v>
@@ -18240,7 +18240,7 @@
         <v>21</v>
       </c>
       <c r="J134" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="K134" t="s">
         <v>1118</v>
@@ -18323,7 +18323,7 @@
         <v>24</v>
       </c>
       <c r="J135" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="K135" t="s">
         <v>1136</v>
@@ -18489,7 +18489,7 @@
         <v>21</v>
       </c>
       <c r="J137" t="s">
-        <v>1092</v>
+        <v>1112</v>
       </c>
       <c r="K137" t="s">
         <v>1115</v>
@@ -18572,7 +18572,7 @@
         <v>21</v>
       </c>
       <c r="J138" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="K138" t="s">
         <v>1136</v>
@@ -18655,7 +18655,7 @@
         <v>21</v>
       </c>
       <c r="J139" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K139" t="s">
         <v>1125</v>
@@ -18738,7 +18738,7 @@
         <v>20</v>
       </c>
       <c r="J140" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="K140" t="s">
         <v>1116</v>
@@ -18821,7 +18821,7 @@
         <v>20</v>
       </c>
       <c r="J141" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="K141" t="s">
         <v>1125</v>
@@ -18904,7 +18904,7 @@
         <v>16</v>
       </c>
       <c r="J142" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K142" t="s">
         <v>1123</v>
@@ -18987,7 +18987,7 @@
         <v>18</v>
       </c>
       <c r="J143" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="K143" t="s">
         <v>1118</v>
@@ -19070,7 +19070,7 @@
         <v>17</v>
       </c>
       <c r="J144" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K144" t="s">
         <v>1123</v>
@@ -19153,7 +19153,7 @@
         <v>17</v>
       </c>
       <c r="J145" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="K145" t="s">
         <v>1136</v>
@@ -19236,7 +19236,7 @@
         <v>22</v>
       </c>
       <c r="J146" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K146" t="s">
         <v>1115</v>
@@ -19319,7 +19319,7 @@
         <v>18</v>
       </c>
       <c r="J147" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K147" t="s">
         <v>1115</v>
@@ -19402,7 +19402,7 @@
         <v>21</v>
       </c>
       <c r="J148" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="K148" t="s">
         <v>1137</v>
@@ -19485,7 +19485,7 @@
         <v>20</v>
       </c>
       <c r="J149" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="K149" t="s">
         <v>1138</v>
@@ -19568,7 +19568,7 @@
         <v>17</v>
       </c>
       <c r="J150" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="K150" t="s">
         <v>1123</v>
@@ -19817,7 +19817,7 @@
         <v>19</v>
       </c>
       <c r="J153" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="K153" t="s">
         <v>1123</v>
@@ -19900,7 +19900,7 @@
         <v>19</v>
       </c>
       <c r="J154" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="K154" t="s">
         <v>1115</v>
@@ -20066,7 +20066,7 @@
         <v>21</v>
       </c>
       <c r="J156" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="K156" t="s">
         <v>1118</v>
@@ -20149,7 +20149,7 @@
         <v>17</v>
       </c>
       <c r="J157" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="K157" t="s">
         <v>1138</v>
@@ -20232,7 +20232,7 @@
         <v>18</v>
       </c>
       <c r="J158" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="K158" t="s">
         <v>1116</v>
@@ -20315,7 +20315,7 @@
         <v>19</v>
       </c>
       <c r="J159" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="K159" t="s">
         <v>1125</v>
@@ -20398,7 +20398,7 @@
         <v>18</v>
       </c>
       <c r="J160" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="K160" t="s">
         <v>1123</v>
@@ -20481,7 +20481,7 @@
         <v>20</v>
       </c>
       <c r="J161" t="s">
-        <v>1092</v>
+        <v>1109</v>
       </c>
       <c r="K161" t="s">
         <v>1138</v>
@@ -20564,7 +20564,7 @@
         <v>20</v>
       </c>
       <c r="J162" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="K162" t="s">
         <v>1115</v>
@@ -20647,7 +20647,7 @@
         <v>22</v>
       </c>
       <c r="J163" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="K163" t="s">
         <v>1119</v>
@@ -20730,7 +20730,7 @@
         <v>20</v>
       </c>
       <c r="J164" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="K164" t="s">
         <v>1123</v>
@@ -20813,7 +20813,7 @@
         <v>19</v>
       </c>
       <c r="J165" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="K165" t="s">
         <v>1136</v>
@@ -25568,7 +25568,7 @@
         <v>6</v>
       </c>
       <c r="J219" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="K219" t="s">
         <v>1119</v>
@@ -32221,7 +32221,7 @@
         <v>14</v>
       </c>
       <c r="J295" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="K295" t="s">
         <v>1116</v>
@@ -33636,7 +33636,7 @@
         <v>7</v>
       </c>
       <c r="J311" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="K311" t="s">
         <v>1116</v>
@@ -37779,7 +37779,7 @@
         <v>6</v>
       </c>
       <c r="J359" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="K359" t="s">
         <v>1119</v>
@@ -43175,7 +43175,7 @@
         <v>10</v>
       </c>
       <c r="J420" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K420" t="s">
         <v>1170</v>
@@ -43590,7 +43590,7 @@
         <v>6</v>
       </c>
       <c r="J425" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K425" t="s">
         <v>1123</v>
@@ -44450,7 +44450,7 @@
         <v>10</v>
       </c>
       <c r="J435" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K435" t="s">
         <v>1115</v>
